--- a/excercise2/classification/RF/RF_top_features_global.xlsx
+++ b/excercise2/classification/RF/RF_top_features_global.xlsx
@@ -1,37 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>importance</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>labour</t>
+  </si>
+  <si>
+    <t>aware</t>
+  </si>
+  <si>
+    <t>confirm</t>
+  </si>
+  <si>
+    <t>congressional</t>
+  </si>
+  <si>
+    <t>think</t>
+  </si>
+  <si>
+    <t>fantastic</t>
+  </si>
+  <si>
+    <t>lady</t>
+  </si>
+  <si>
+    <t>shadow</t>
+  </si>
+  <si>
+    <t>happen</t>
+  </si>
+  <si>
+    <t>meet</t>
+  </si>
+  <si>
+    <t>recognise</t>
+  </si>
+  <si>
+    <t>britain</t>
+  </si>
+  <si>
+    <t>concern</t>
+  </si>
+  <si>
+    <t>scottish</t>
+  </si>
+  <si>
+    <t>constituency</t>
+  </si>
+  <si>
+    <t>absolutely</t>
+  </si>
+  <si>
+    <t>discuss</t>
+  </si>
+  <si>
+    <t>page</t>
+  </si>
+  <si>
+    <t>statement</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +123,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,292 +439,242 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>importance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>hear</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.016314090215107</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>honor</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.013817138187509</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>shadow</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0137812141113148</v>
-      </c>
-      <c r="C4" t="n">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mention</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.01363737535560953</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B2">
+        <v>0.02306964960734722</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>absolutely</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.01320195386671555</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B3">
+        <v>0.0168782539488536</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>rightly</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0130524603159584</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B4">
+        <v>0.0166806948381287</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>program</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.01246208387487145</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B5">
+        <v>0.0157473181809771</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>scheme</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.01187341148551546</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B6">
+        <v>0.01561073985922914</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>labour</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.01176930206885845</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B7">
+        <v>0.01519664652674084</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>huge</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.0114680574684317</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B8">
+        <v>0.01513573439172596</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ministers</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.01138059247672797</v>
-      </c>
-      <c r="C12" t="n">
+      <c r="B9">
+        <v>0.01422748421267526</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>fantastic</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.01086992920383761</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B10">
+        <v>0.01284788365594509</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>quite</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.01060044940032394</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B11">
+        <v>0.0123818478137746</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.009999048175600827</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B12">
+        <v>0.01193222012478305</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.009719997979428583</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B13">
+        <v>0.0115745700142292</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>fail</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.009631536893522578</v>
-      </c>
-      <c r="C17" t="n">
+      <c r="B14">
+        <v>0.01140847977668753</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>let</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.009381053197591466</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B15">
+        <v>0.01108945682350483</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lot</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.009351574872194582</v>
-      </c>
-      <c r="C19" t="n">
+      <c r="B16">
+        <v>0.01093703894926315</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>really</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.009192944338949681</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="B17">
+        <v>0.01078074960846786</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>california</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.009011579525460906</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B18">
+        <v>0.009968368356754615</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
+      <c r="B19">
+        <v>0.009909186571072729</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>0.009857638895045923</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>0.009631680658812258</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>